--- a/output/pdf_financials_xlsx/TN.xlsx
+++ b/output/pdf_financials_xlsx/TN.xlsx
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.08652799999999999</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.083776</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.050362</v>
       </c>
     </row>
     <row r="92">
@@ -3175,7 +3175,11 @@
           <t>Foreign translation reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.08652799999999999</v>
       </c>

--- a/output/pdf_financials_xlsx/TN.xlsx
+++ b/output/pdf_financials_xlsx/TN.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005275</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001481</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001778</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005275</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001481</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001778</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.032277</v>
+        <v>5.027002</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.284778</v>
+        <v>4.283297</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.437415</v>
+        <v>2.435637</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/TN.xlsx
+++ b/output/pdf_financials_xlsx/TN.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.557717</v>
+        <v>0.665717</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.62588</v>
+        <v>0.73388</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.524728</v>
+        <v>0.632728</v>
       </c>
     </row>
     <row r="8">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.585</v>
+        <v>-0.585</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>2.828642</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.7738969999999999</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.838928</v>
       </c>
     </row>
     <row r="116">
@@ -3709,7 +3709,11 @@
           <t>Proceeds from sale of investments (note 6)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>2.828642</v>
       </c>
@@ -4071,7 +4075,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>-0.585</v>
       </c>
@@ -4224,7 +4232,11 @@
           <t>Director fees (note 11)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>0.108</v>
       </c>
@@ -4830,7 +4842,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>0.585</v>
       </c>
